--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/ELAN/ELAN+50T+50EP+optim_purn/params_vs_psnr_analysis/ELAN_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/ELAN/ELAN+50T+50EP+optim_purn/params_vs_psnr_analysis/ELAN_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>884592</v>
       </c>
       <c r="C2" t="n">
+        <v>2.124024012</v>
+      </c>
+      <c r="D2" t="n">
         <v>27.66504058837891</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>1043548</v>
       </c>
       <c r="C3" t="n">
+        <v>2.268395712</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.0554084777832</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>1619936</v>
       </c>
       <c r="C4" t="n">
+        <v>4.067064</v>
+      </c>
+      <c r="D4" t="n">
         <v>28.07649307250977</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>485596</v>
       </c>
       <c r="C5" t="n">
+        <v>1.444006656</v>
+      </c>
+      <c r="D5" t="n">
         <v>29.84953155517578</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>1338450</v>
       </c>
       <c r="C6" t="n">
+        <v>3.836590272</v>
+      </c>
+      <c r="D6" t="n">
         <v>30.53452568054199</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>2055918</v>
       </c>
       <c r="C7" t="n">
+        <v>4.95144414</v>
+      </c>
+      <c r="D7" t="n">
         <v>28.18730812072754</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>732952</v>
       </c>
       <c r="C8" t="n">
+        <v>1.59994296</v>
+      </c>
+      <c r="D8" t="n">
         <v>27.87917518615723</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>497032</v>
       </c>
       <c r="C9" t="n">
+        <v>1.444006656</v>
+      </c>
+      <c r="D9" t="n">
         <v>27.95033226013184</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>602036</v>
       </c>
       <c r="C10" t="n">
+        <v>1.357007616</v>
+      </c>
+      <c r="D10" t="n">
         <v>29.32700309753418</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>941842</v>
       </c>
       <c r="C11" t="n">
+        <v>2.81829816</v>
+      </c>
+      <c r="D11" t="n">
         <v>30.03757743835449</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>941842</v>
       </c>
       <c r="C12" t="n">
+        <v>2.81829816</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.30857734680176</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1131326</v>
       </c>
       <c r="C13" t="n">
+        <v>3.308501196</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.3171802520752</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>933036</v>
       </c>
       <c r="C14" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.43386116027832</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>933036</v>
       </c>
       <c r="C15" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.35392265319824</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>933036</v>
       </c>
       <c r="C16" t="n">
+        <v>2.97678078</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.37254409790039</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>2190456</v>
       </c>
       <c r="C17" t="n">
+        <v>6.26621688</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.13906059265137</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>1371564</v>
       </c>
       <c r="C18" t="n">
+        <v>4.15235502</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.50540199279785</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>1623048</v>
       </c>
       <c r="C19" t="n">
+        <v>4.81024224</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.64372634887695</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>1602440</v>
       </c>
       <c r="C20" t="n">
+        <v>3.621157056</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.35832939147949</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>1805618</v>
       </c>
       <c r="C21" t="n">
+        <v>5.006426544</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.52601699829102</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>1131326</v>
       </c>
       <c r="C22" t="n">
+        <v>3.308501196</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.39954299926758</v>
       </c>
     </row>
